--- a/submission/Group Formation/STA380GroupForm.xlsx
+++ b/submission/Group Formation/STA380GroupForm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\49482\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/380_group_project/sta380-group-project/submission/Group Formation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8977763-ABF1-4590-AE9A-9E77F55C3BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA01D63A-519B-A44D-B780-A27EEE3DB1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2172" yWindow="2172" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1400" yWindow="2160" windowWidth="23860" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -98,13 +98,24 @@
   </si>
   <si>
     <t>https://github.com/clara0510huang/sta380-group-project.git</t>
+  </si>
+  <si>
+    <t>Dongshuo Yang</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>yangdo35</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://github.com/yangdo35</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -115,6 +126,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -123,6 +135,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -130,6 +143,21 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -159,12 +187,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -384,17 +413,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="31.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" customWidth="1"/>
-    <col min="3" max="3" width="15.21875" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -402,12 +431,12 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -415,67 +444,67 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1"/>
       <c r="B20" s="3" t="s">
         <v>8</v>
@@ -493,7 +522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
@@ -513,47 +542,63 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22">
+        <v>1007867202</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/submission/Group Formation/STA380GroupForm.xlsx
+++ b/submission/Group Formation/STA380GroupForm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/380_group_project/sta380-group-project/submission/Group Formation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA01D63A-519B-A44D-B780-A27EEE3DB1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84963E41-4DA3-844D-AAEE-69061CD5B4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1400" yWindow="2160" windowWidth="23860" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -187,13 +187,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -412,7 +425,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="31.6640625" customWidth="1"/>
@@ -496,106 +509,253 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="3" t="s">
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="6">
         <v>1007049677</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="3" t="s">
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="6">
         <v>1007867202</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="3" t="s">
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="3" t="s">
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="3" t="s">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="4" t="s">
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="4" t="s">
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="8" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="4" t="s">
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="4" t="s">
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="8" t="s">
         <v>21</v>
       </c>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>

--- a/submission/Group Formation/STA380GroupForm.xlsx
+++ b/submission/Group Formation/STA380GroupForm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/380_group_project/sta380-group-project/submission/Group Formation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84963E41-4DA3-844D-AAEE-69061CD5B4F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA27A870-CB49-014E-8901-CF206164CA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1400" yWindow="2160" windowWidth="23860" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -97,9 +97,6 @@
     <t>clara0510huang</t>
   </si>
   <si>
-    <t>https://github.com/clara0510huang/sta380-group-project.git</t>
-  </si>
-  <si>
     <t>Dongshuo Yang</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -109,6 +106,9 @@
   </si>
   <si>
     <t>https://github.com/yangdo35</t>
+  </si>
+  <si>
+    <t>https://github.com/clara0510huang</t>
   </si>
 </sst>
 </file>
@@ -556,7 +556,7 @@
         <v>24</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -568,19 +568,19 @@
         <v>14</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="D22" s="6">
         <v>1007867202</v>
       </c>
       <c r="E22" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>27</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>

--- a/submission/Group Formation/STA380GroupForm.xlsx
+++ b/submission/Group Formation/STA380GroupForm.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/380_group_project/sta380-group-project/submission/Group Formation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\49482\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA27A870-CB49-014E-8901-CF206164CA18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE00BA61-193D-4176-9DDA-C09130CEF63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1400" yWindow="2160" windowWidth="23860" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterate="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -109,13 +109,19 @@
   </si>
   <si>
     <t>https://github.com/clara0510huang</t>
+  </si>
+  <si>
+    <t>Inverse-Transform Method</t>
+  </si>
+  <si>
+    <t>Exponential + Normal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -426,17 +432,17 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.1640625" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -444,12 +450,12 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="1"/>
       <c r="B4" s="3" t="s">
         <v>2</v>
@@ -457,67 +463,73 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="3"/>
     </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="3"/>
     </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
     </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1">
       <c r="A14" s="3"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:4" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10" ht="15.75" customHeight="1">
       <c r="A18" s="3"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="4"/>
       <c r="B20" s="5" t="s">
         <v>8</v>
@@ -539,7 +551,7 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="5" t="s">
         <v>13</v>
       </c>
@@ -563,7 +575,7 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="5" t="s">
         <v>14</v>
       </c>
@@ -587,7 +599,7 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="5" t="s">
         <v>15</v>
       </c>
@@ -601,7 +613,7 @@
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="5" t="s">
         <v>16</v>
       </c>
@@ -615,7 +627,7 @@
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="5" t="s">
         <v>17</v>
       </c>
@@ -629,7 +641,7 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10" ht="15.75" customHeight="1">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -641,7 +653,7 @@
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10" ht="15.75" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>18</v>
       </c>
@@ -655,7 +667,7 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10" ht="15.75" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>19</v>
       </c>
@@ -669,7 +681,7 @@
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>20</v>
       </c>
@@ -683,7 +695,7 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>21</v>
       </c>
@@ -697,7 +709,7 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -709,7 +721,7 @@
       <c r="I31" s="6"/>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -721,7 +733,7 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -733,7 +745,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -745,7 +757,7 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
     </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>

--- a/submission/Group Formation/STA380GroupForm.xlsx
+++ b/submission/Group Formation/STA380GroupForm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\49482\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026 winter\sta380\380project\sta380-group-project\submission\Group Formation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE00BA61-193D-4176-9DDA-C09130CEF63F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16E2990-F560-40CE-AC01-EE1E41EEEA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1215" yWindow="3960" windowWidth="28800" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -115,6 +115,24 @@
   </si>
   <si>
     <t>Exponential + Normal</t>
+  </si>
+  <si>
+    <t>Qi Wang</t>
+  </si>
+  <si>
+    <t>wangq388</t>
+  </si>
+  <si>
+    <t>https://github.com/mdfkgtm</t>
+  </si>
+  <si>
+    <t>mdfkgtm</t>
+  </si>
+  <si>
+    <t>Bootstrap Estimate</t>
+  </si>
+  <si>
+    <t>Linear regression + Mean variance</t>
   </si>
 </sst>
 </file>
@@ -193,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -213,9 +231,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -432,14 +451,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="1" max="1" width="31.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1">
@@ -488,10 +507,16 @@
       <c r="A10" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1">
@@ -603,11 +628,21 @@
       <c r="A23" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
+      <c r="B23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="6">
+        <v>1010643715</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="G23" s="6"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>

--- a/submission/Group Formation/STA380GroupForm.xlsx
+++ b/submission/Group Formation/STA380GroupForm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026 winter\sta380\380project\sta380-group-project\submission\Group Formation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B16E2990-F560-40CE-AC01-EE1E41EEEA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296314D6-CC96-44FD-A484-D27FB2CA7249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1215" yWindow="3960" windowWidth="28800" windowHeight="15330" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -132,7 +132,10 @@
     <t>Bootstrap Estimate</t>
   </si>
   <si>
-    <t>Linear regression + Mean variance</t>
+    <t xml:space="preserve">Linear regression </t>
+  </si>
+  <si>
+    <t>Mean variance</t>
   </si>
 </sst>
 </file>
@@ -211,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -231,7 +234,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,6 +525,9 @@
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
@@ -640,7 +645,7 @@
       <c r="E23" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" t="s">
         <v>33</v>
       </c>
       <c r="G23" s="6"/>

--- a/submission/Group Formation/STA380GroupForm.xlsx
+++ b/submission/Group Formation/STA380GroupForm.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -25,12 +25,21 @@
     <t>Topic Number 1</t>
   </si>
   <si>
+    <t>Monte Carlo of a Hypothesis Test</t>
+  </si>
+  <si>
     <t>Simulated distributions, if applicable:</t>
   </si>
   <si>
+    <t>Normal distribution</t>
+  </si>
+  <si>
     <t>Extra details:</t>
   </si>
   <si>
+    <t>one Sample t test for  population</t>
+  </si>
+  <si>
     <t>Topic Number 2</t>
   </si>
   <si>
@@ -113,6 +122,23 @@
   </si>
   <si>
     <t>Jiawei Cao</t>
+  </si>
+  <si>
+    <t>caojiaw5</t>
+  </si>
+  <si>
+    <t>Jiaweiii77</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u val="single"/>
+        <sz val="10"/>
+        <color indexed="12"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>https://github.com/Jiaweiii77</t>
+    </r>
   </si>
   <si>
     <t>Student 5</t>
@@ -137,7 +163,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -166,8 +192,14 @@
       <color indexed="8"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,6 +209,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="11"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -307,7 +345,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -323,25 +361,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -353,49 +391,52 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -417,6 +458,8 @@
       <rgbColor rgb="ff000000"/>
       <rgbColor rgb="ffc9daf8"/>
       <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ff0000ff"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -615,17 +658,17 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -653,10 +696,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Arial"/>
-            <a:ea typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-            <a:sym typeface="Arial"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -904,12 +947,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -1196,7 +1239,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1224,10 +1267,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Arial"/>
-            <a:ea typeface="Arial"/>
-            <a:cs typeface="Arial"/>
-            <a:sym typeface="Arial"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1549,7 +1592,9 @@
       <c r="A5" t="s" s="7">
         <v>3</v>
       </c>
-      <c r="B5" s="8"/>
+      <c r="B5" t="s" s="15">
+        <v>4</v>
+      </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="6"/>
@@ -1561,9 +1606,11 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" t="s" s="7">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5"/>
+        <v>5</v>
+      </c>
+      <c r="B6" t="s" s="16">
+        <v>6</v>
+      </c>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -1575,9 +1622,11 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" t="s" s="7">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5"/>
+        <v>7</v>
+      </c>
+      <c r="B7" t="s" s="16">
+        <v>8</v>
+      </c>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -1588,7 +1637,7 @@
       <c r="J7" s="6"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="15"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="5"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
@@ -1600,7 +1649,7 @@
       <c r="J8" s="6"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="15"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -1613,10 +1662,10 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" t="s" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s" s="16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -1629,10 +1678,10 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" t="s" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s" s="16">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -1645,10 +1694,10 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" t="s" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s" s="16">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -1660,7 +1709,7 @@
       <c r="J12" s="6"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="15"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -1672,7 +1721,7 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="15"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -1685,10 +1734,10 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" t="s" s="7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s" s="16">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -1701,10 +1750,10 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" t="s" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s" s="16">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1717,7 +1766,7 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" t="s" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
@@ -1730,7 +1779,7 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="15"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -1754,258 +1803,269 @@
       <c r="J19" s="6"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="17"/>
-      <c r="B20" t="s" s="18">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s" s="18">
-        <v>14</v>
-      </c>
-      <c r="D20" t="s" s="18">
-        <v>15</v>
-      </c>
-      <c r="E20" t="s" s="18">
+      <c r="A20" s="18"/>
+      <c r="B20" t="s" s="19">
         <v>16</v>
       </c>
-      <c r="F20" t="s" s="18">
+      <c r="C20" t="s" s="19">
         <v>17</v>
       </c>
-      <c r="G20" s="19"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
+      <c r="D20" t="s" s="19">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s" s="19">
+        <v>19</v>
+      </c>
+      <c r="F20" t="s" s="19">
+        <v>20</v>
+      </c>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" t="s" s="21">
-        <v>18</v>
-      </c>
-      <c r="B21" t="s" s="22">
-        <v>19</v>
-      </c>
-      <c r="C21" t="s" s="23">
-        <v>20</v>
-      </c>
-      <c r="D21" s="24">
+      <c r="A21" t="s" s="22">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s" s="23">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s" s="24">
+        <v>23</v>
+      </c>
+      <c r="D21" s="25">
         <v>1007049677</v>
       </c>
-      <c r="E21" t="s" s="23">
-        <v>21</v>
-      </c>
-      <c r="F21" t="s" s="23">
-        <v>22</v>
-      </c>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
+      <c r="E21" t="s" s="24">
+        <v>24</v>
+      </c>
+      <c r="F21" t="s" s="24">
+        <v>25</v>
+      </c>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" t="s" s="21">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s" s="25">
-        <v>24</v>
-      </c>
-      <c r="C22" t="s" s="26">
-        <v>25</v>
-      </c>
-      <c r="D22" s="27">
+      <c r="A22" t="s" s="22">
+        <v>26</v>
+      </c>
+      <c r="B22" t="s" s="26">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s" s="27">
+        <v>28</v>
+      </c>
+      <c r="D22" s="28">
         <v>1007867202</v>
       </c>
-      <c r="E22" t="s" s="26">
-        <v>25</v>
-      </c>
-      <c r="F22" t="s" s="26">
-        <v>26</v>
-      </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
+      <c r="E22" t="s" s="27">
+        <v>28</v>
+      </c>
+      <c r="F22" t="s" s="27">
+        <v>29</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" t="s" s="21">
-        <v>27</v>
-      </c>
-      <c r="B23" t="s" s="25">
-        <v>28</v>
-      </c>
-      <c r="C23" t="s" s="26">
-        <v>29</v>
-      </c>
-      <c r="D23" s="27">
+      <c r="A23" t="s" s="22">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s" s="26">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s" s="27">
+        <v>32</v>
+      </c>
+      <c r="D23" s="28">
         <v>1010643715</v>
       </c>
-      <c r="E23" t="s" s="26">
-        <v>30</v>
-      </c>
-      <c r="F23" t="s" s="28">
-        <v>31</v>
-      </c>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
+      <c r="E23" t="s" s="27">
+        <v>33</v>
+      </c>
+      <c r="F23" t="s" s="29">
+        <v>34</v>
+      </c>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" t="s" s="21">
-        <v>32</v>
-      </c>
-      <c r="B24" t="s" s="25">
-        <v>33</v>
-      </c>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
+      <c r="A24" t="s" s="22">
+        <v>35</v>
+      </c>
+      <c r="B24" t="s" s="26">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s" s="27">
+        <v>37</v>
+      </c>
+      <c r="D24" s="28">
+        <v>1008092261</v>
+      </c>
+      <c r="E24" t="s" s="27">
+        <v>38</v>
+      </c>
+      <c r="F24" t="s" s="27">
+        <v>39</v>
+      </c>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" t="s" s="21">
-        <v>34</v>
-      </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
+      <c r="A25" t="s" s="22">
+        <v>40</v>
+      </c>
+      <c r="B25" s="20"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="29"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" t="s" s="26">
-        <v>35</v>
-      </c>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
+      <c r="A27" t="s" s="27">
+        <v>41</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" t="s" s="26">
-        <v>36</v>
-      </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
+      <c r="A28" t="s" s="27">
+        <v>42</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" t="s" s="26">
-        <v>37</v>
-      </c>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
+      <c r="A29" t="s" s="27">
+        <v>43</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" t="s" s="26">
-        <v>38</v>
-      </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
+      <c r="A30" t="s" s="27">
+        <v>44</v>
+      </c>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
+      <c r="J32" s="21"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="20"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="20"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
+      <c r="H34" s="21"/>
+      <c r="I34" s="21"/>
+      <c r="J34" s="21"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="20"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F24" r:id="rId1" location="" tooltip="" display="https://github.com/Jiaweiii77"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>

--- a/submission/Group Formation/STA380GroupForm.xlsx
+++ b/submission/Group Formation/STA380GroupForm.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/380_group_project/sta380-group-project/submission/Group Formation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB23F84-649A-D747-BE48-202876522FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="920" yWindow="2320" windowWidth="30140" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -25,21 +34,12 @@
     <t>Topic Number 1</t>
   </si>
   <si>
-    <t>Monte Carlo of a Hypothesis Test</t>
-  </si>
-  <si>
     <t>Simulated distributions, if applicable:</t>
   </si>
   <si>
-    <t>Normal distribution</t>
-  </si>
-  <si>
     <t>Extra details:</t>
   </si>
   <si>
-    <t>one Sample t test for  population</t>
-  </si>
-  <si>
     <t>Topic Number 2</t>
   </si>
   <si>
@@ -116,9 +116,6 @@
   </si>
   <si>
     <t>https://github.com/mdfkgtm</t>
-  </si>
-  <si>
-    <t>Student 4</t>
   </si>
   <si>
     <t>Jiawei Cao</t>
@@ -132,10 +129,11 @@
   <si>
     <r>
       <rPr>
-        <u val="single"/>
+        <u/>
         <sz val="10"/>
         <color indexed="12"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>https://github.com/Jiaweiii77</t>
     </r>
@@ -154,49 +152,75 @@
   </si>
   <si>
     <t>To report an inactive member, please refer to the "Reporting Inactive Members" section under the project description.</t>
+  </si>
+  <si>
+    <t>Autoregressive, AR(1), MA, time series models</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monte Carlo Simulation</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Extra details:</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Student 4</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>This simulation will be focusing on AR(1) and ARMA processes, for the study of the parameters' impact</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>on stationary, and verifying autocorrelation structures.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="1"/>
+      <b/>
+      <i/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <u val="single"/>
+      <u/>
       <sz val="10"/>
       <color indexed="12"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="FangSong"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -219,7 +243,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -339,134 +363,178 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="37">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="31">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffc9daf8"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFC9DAF8"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -668,7 +736,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -687,7 +755,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -717,7 +785,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -743,7 +811,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -769,7 +837,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -795,7 +863,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -821,7 +889,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -847,7 +915,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -873,7 +941,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -899,7 +967,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -925,7 +993,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -938,9 +1006,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -957,7 +1031,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -976,7 +1050,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1002,7 +1076,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1028,7 +1102,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1054,7 +1128,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1080,7 +1154,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1106,7 +1180,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1132,7 +1206,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1158,7 +1232,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1184,7 +1258,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1210,7 +1284,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1223,9 +1297,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1239,7 +1319,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1258,7 +1338,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1288,7 +1368,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1314,7 +1394,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1340,7 +1420,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1366,7 +1446,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1392,7 +1472,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1418,7 +1498,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1444,7 +1524,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1470,7 +1550,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1496,7 +1576,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1509,34 +1589,41 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="31.6719" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6719" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.1719" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1719" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.3516" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1719" style="1" customWidth="1"/>
-    <col min="7" max="10" width="12.6719" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="12.6719" style="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" style="1" customWidth="1"/>
+    <col min="7" max="11" width="12.6640625" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2"/>
-      <c r="B1" t="s" s="3">
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="4"/>
@@ -1548,8 +1635,8 @@
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" t="s" s="7">
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="8"/>
@@ -1562,7 +1649,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" ht="13.65" customHeight="1">
+    <row r="3" spans="1:10" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -1574,9 +1661,9 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
-      <c r="B4" t="s" s="13">
+      <c r="B4" s="13" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="14"/>
@@ -1588,12 +1675,12 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" t="s" s="7">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s" s="15">
-        <v>4</v>
+      <c r="B5" s="30" t="s">
+        <v>42</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -1604,15 +1691,15 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" t="s" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s" s="16">
-        <v>6</v>
-      </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="36"/>
+      <c r="D6" s="35"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -1620,36 +1707,35 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" t="s" s="7">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s" s="16">
-        <v>8</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>45</v>
+      </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="17"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="16"/>
+      <c r="B8" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="33"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="17"/>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="16"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
@@ -1660,12 +1746,12 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" t="s" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s" s="16">
-        <v>10</v>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>7</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -1676,12 +1762,12 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" t="s" s="7">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s" s="16">
-        <v>11</v>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>8</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -1692,12 +1778,12 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" t="s" s="7">
-        <v>7</v>
-      </c>
-      <c r="B12" t="s" s="16">
-        <v>12</v>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>9</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -1708,8 +1794,8 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="17"/>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="16"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -1720,8 +1806,8 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="17"/>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="16"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -1732,12 +1818,12 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" t="s" s="7">
-        <v>13</v>
-      </c>
-      <c r="B15" t="s" s="16">
-        <v>14</v>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>11</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -1748,12 +1834,12 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" t="s" s="7">
-        <v>5</v>
-      </c>
-      <c r="B16" t="s" s="16">
-        <v>15</v>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="15" t="s">
+        <v>12</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1764,9 +1850,9 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" t="s" s="7">
-        <v>7</v>
+    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="7" t="s">
+        <v>5</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
@@ -1778,8 +1864,8 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="17"/>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="16"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
@@ -1790,7 +1876,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" ht="13.65" customHeight="1">
+    <row r="19" spans="1:10" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -1802,272 +1888,277 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="18"/>
-      <c r="B20" t="s" s="19">
+    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="17"/>
+      <c r="B20" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C20" t="s" s="19">
+      <c r="F20" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D20" t="s" s="19">
+      <c r="G20" s="19"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E20" t="s" s="19">
+      <c r="B21" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F20" t="s" s="19">
+      <c r="C21" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="20"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" t="s" s="22">
+      <c r="D21" s="24">
+        <v>1007049677</v>
+      </c>
+      <c r="E21" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B21" t="s" s="23">
+      <c r="F21" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s" s="24">
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="25">
-        <v>1007049677</v>
-      </c>
-      <c r="E21" t="s" s="24">
+      <c r="B22" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="F21" t="s" s="24">
+      <c r="C22" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" t="s" s="22">
+      <c r="D22" s="27">
+        <v>1007867202</v>
+      </c>
+      <c r="E22" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="B22" t="s" s="26">
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C22" t="s" s="27">
+      <c r="B23" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="28">
-        <v>1007867202</v>
-      </c>
-      <c r="E22" t="s" s="27">
-        <v>28</v>
-      </c>
-      <c r="F22" t="s" s="27">
+      <c r="C23" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="21"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" t="s" s="22">
+      <c r="D23" s="27">
+        <v>1010643715</v>
+      </c>
+      <c r="E23" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="B23" t="s" s="26">
+      <c r="F23" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C23" t="s" s="27">
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D23" s="28">
-        <v>1010643715</v>
-      </c>
-      <c r="E23" t="s" s="27">
+      <c r="C24" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="F23" t="s" s="29">
+      <c r="D24" s="27">
+        <v>1008092261</v>
+      </c>
+      <c r="E24" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" t="s" s="22">
+      <c r="F24" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B24" t="s" s="26">
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C24" t="s" s="27">
+      <c r="B25" s="19"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="29"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="28">
-        <v>1008092261</v>
-      </c>
-      <c r="E24" t="s" s="27">
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="F24" t="s" s="27">
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
-      <c r="J24" s="21"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" t="s" s="22">
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A30" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="20"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
-      <c r="J25" s="21"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="30"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" t="s" s="27">
-        <v>41</v>
-      </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" t="s" s="27">
-        <v>42</v>
-      </c>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" t="s" s="27">
-        <v>43</v>
-      </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" t="s" s="27">
-        <v>44</v>
-      </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="21"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="21"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="21"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="21"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="21"/>
-      <c r="B34" s="21"/>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="21"/>
-      <c r="H34" s="21"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="21"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="21"/>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
-      <c r="G35" s="21"/>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F24" r:id="rId1" location="" tooltip="" display="https://github.com/Jiaweiii77"/>
+    <hyperlink ref="F24" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/submission/Group Formation/STA380GroupForm.xlsx
+++ b/submission/Group Formation/STA380GroupForm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/380_group_project/sta380-group-project/submission/Group Formation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\49482\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB23F84-649A-D747-BE48-202876522FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5443E9-B744-453C-8FEE-7F4ACF50713F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="2320" windowWidth="30140" windowHeight="18080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -49,16 +49,10 @@
     <t xml:space="preserve">Linear regression </t>
   </si>
   <si>
-    <t>Mean variance</t>
-  </si>
-  <si>
     <t>Topic Number 3</t>
   </si>
   <si>
     <t>Inverse-Transform Method</t>
-  </si>
-  <si>
-    <t>Exponential + Normal</t>
   </si>
   <si>
     <t>Name</t>
@@ -177,12 +171,24 @@
     <t>on stationary, and verifying autocorrelation structures.</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
+  <si>
+    <t>Exponential + Gamma</t>
+  </si>
+  <si>
+    <t>This project uses the Boston Housing Dataset to study the bootstrap estimation of linear regression coefficients (β₀, β₁),</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> focusing on their mean and variance properties. </t>
+  </si>
+  <si>
+    <t>We will compare bootstrap-derived estimates with theoretical OLS results and examine how it affects estimation stability.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -437,17 +443,17 @@
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1609,19 +1615,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" style="1" customWidth="1"/>
     <col min="7" max="11" width="12.6640625" style="1" customWidth="1"/>
     <col min="12" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1635,7 +1641,7 @@
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -1649,7 +1655,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:10" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" ht="13.8" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -1661,7 +1667,7 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1">
       <c r="A4" s="12"/>
       <c r="B4" s="13" t="s">
         <v>2</v>
@@ -1675,12 +1681,12 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -1691,15 +1697,15 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="36"/>
-      <c r="D6" s="35"/>
+      <c r="B6" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="35"/>
+      <c r="D6" s="36"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -1707,12 +1713,12 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="31" t="s">
         <v>43</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>45</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -1720,21 +1726,21 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="16"/>
-      <c r="B8" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="33"/>
+      <c r="B8" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="34"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="A9" s="16"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
@@ -1746,7 +1752,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>6</v>
       </c>
@@ -1762,7 +1768,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>4</v>
       </c>
@@ -1778,12 +1784,12 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
       <c r="A12" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
@@ -1794,9 +1800,11 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
       <c r="A13" s="16"/>
-      <c r="B13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -1806,9 +1814,11 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
       <c r="A14" s="16"/>
-      <c r="B14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -1818,12 +1828,12 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
       <c r="A15" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>10</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>11</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -1834,12 +1844,12 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
       <c r="A16" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1850,7 +1860,7 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10" ht="15.75" customHeight="1">
       <c r="A17" s="7" t="s">
         <v>5</v>
       </c>
@@ -1864,7 +1874,7 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10" ht="15.75" customHeight="1">
       <c r="A18" s="16"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
@@ -1876,7 +1886,7 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10" ht="13.8" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -1888,127 +1898,127 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="17"/>
       <c r="B20" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="E20" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="F20" s="18" t="s">
         <v>15</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>17</v>
       </c>
       <c r="G20" s="19"/>
       <c r="H20" s="20"/>
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="23" t="s">
         <v>18</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>20</v>
       </c>
       <c r="D21" s="24">
         <v>1007049677</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G21" s="20"/>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="26" t="s">
         <v>23</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>25</v>
       </c>
       <c r="D22" s="27">
         <v>1007867202</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>27</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>29</v>
       </c>
       <c r="D23" s="27">
         <v>1010643715</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G23" s="20"/>
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D24" s="27">
         <v>1008092261</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G24" s="20"/>
       <c r="H24" s="20"/>
       <c r="I24" s="20"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="20"/>
@@ -2020,7 +2030,7 @@
       <c r="I25" s="20"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10" ht="15.75" customHeight="1">
       <c r="A26" s="29"/>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -2032,9 +2042,9 @@
       <c r="I26" s="20"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10" ht="15.75" customHeight="1">
       <c r="A27" s="26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -2046,9 +2056,9 @@
       <c r="I27" s="20"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10" ht="15.75" customHeight="1">
       <c r="A28" s="26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -2060,9 +2070,9 @@
       <c r="I28" s="20"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
@@ -2074,9 +2084,9 @@
       <c r="I29" s="20"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
@@ -2088,7 +2098,7 @@
       <c r="I30" s="20"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="20"/>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -2100,7 +2110,7 @@
       <c r="I31" s="20"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="20"/>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -2112,7 +2122,7 @@
       <c r="I32" s="20"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="20"/>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -2124,7 +2134,7 @@
       <c r="I33" s="20"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="20"/>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -2136,7 +2146,7 @@
       <c r="I34" s="20"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="20"/>
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>

--- a/submission/Group Formation/STA380GroupForm.xlsx
+++ b/submission/Group Formation/STA380GroupForm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\49482\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/380_group_project/sta380-group-project/submission/Group Formation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5443E9-B744-453C-8FEE-7F4ACF50713F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14049626-01D0-FA4E-97C2-AAD5108E48B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1000" yWindow="4360" windowWidth="28400" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -183,12 +183,20 @@
   <si>
     <t>We will compare bootstrap-derived estimates with theoretical OLS results and examine how it affects estimation stability.</t>
   </si>
+  <si>
+    <t xml:space="preserve">We will use inverse-transformation method to simulate exponential and gamma distribution, including the </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>graph of true density. Outputing the mean and variance to the theoretical values.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -249,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -380,11 +388,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -454,6 +482,21 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1614,20 +1657,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:J36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="31.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" style="1" customWidth="1"/>
     <col min="7" max="11" width="12.6640625" style="1" customWidth="1"/>
     <col min="12" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2"/>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -1641,7 +1684,7 @@
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
     </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1">
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
@@ -1655,7 +1698,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:10" ht="13.8" customHeight="1">
+    <row r="3" spans="1:10" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="11"/>
       <c r="C3" s="11"/>
@@ -1667,7 +1710,7 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
     </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1">
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12"/>
       <c r="B4" s="13" t="s">
         <v>2</v>
@@ -1681,7 +1724,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1">
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
@@ -1697,7 +1740,7 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
@@ -1713,7 +1756,7 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7" t="s">
         <v>41</v>
       </c>
@@ -1726,7 +1769,7 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="16"/>
       <c r="B8" s="32" t="s">
         <v>44</v>
@@ -1740,7 +1783,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="16"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6"/>
@@ -1752,7 +1795,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7" t="s">
         <v>6</v>
       </c>
@@ -1768,7 +1811,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" ht="15.75" customHeight="1">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7" t="s">
         <v>4</v>
       </c>
@@ -1784,7 +1827,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10" ht="15.75" customHeight="1">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7" t="s">
         <v>5</v>
       </c>
@@ -1800,7 +1843,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" ht="15.75" customHeight="1">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="16"/>
       <c r="B13" s="5" t="s">
         <v>47</v>
@@ -1814,7 +1857,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="16"/>
       <c r="B14" s="5" t="s">
         <v>48</v>
@@ -1828,13 +1871,9 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>10</v>
-      </c>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="16"/>
+      <c r="B15" s="5"/>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -1844,12 +1883,12 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" ht="15.75" customHeight="1">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="7" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -1860,11 +1899,13 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" ht="15.75" customHeight="1">
+    <row r="17" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>45</v>
+      </c>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -1874,165 +1915,171 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A18" s="16"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B18" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="38"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" ht="13.8" customHeight="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+    <row r="19" spans="1:10" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="16"/>
+      <c r="B19" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="43"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A20" s="17"/>
-      <c r="B20" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>15</v>
-      </c>
+    <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="10"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
       <c r="G20" s="19"/>
       <c r="H20" s="20"/>
       <c r="I20" s="20"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A21" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="24">
-        <v>1007049677</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>20</v>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>15</v>
       </c>
       <c r="G21" s="20"/>
       <c r="H21" s="20"/>
       <c r="I21" s="20"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="1:10" ht="15.75" customHeight="1">
+    <row r="22" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="27">
-        <v>1007867202</v>
-      </c>
-      <c r="E22" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="F22" s="26" t="s">
-        <v>24</v>
+        <v>16</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="24">
+        <v>1007049677</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="20"/>
       <c r="I22" s="20"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1">
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="21" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D23" s="27">
-        <v>1010643715</v>
+        <v>1007867202</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="28" t="s">
-        <v>29</v>
+        <v>23</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>24</v>
       </c>
       <c r="G23" s="20"/>
       <c r="H23" s="20"/>
       <c r="I23" s="20"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" customHeight="1">
+    <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="21" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D24" s="27">
-        <v>1008092261</v>
+        <v>1010643715</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="26" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>29</v>
       </c>
       <c r="G24" s="20"/>
       <c r="H24" s="20"/>
       <c r="I24" s="20"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="1:10" ht="15.75" customHeight="1">
+    <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
+        <v>42</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="27">
+        <v>1008092261</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>33</v>
+      </c>
       <c r="G25" s="20"/>
       <c r="H25" s="20"/>
       <c r="I25" s="20"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A26" s="29"/>
-      <c r="B26" s="20"/>
+    <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="19"/>
       <c r="C26" s="20"/>
       <c r="D26" s="20"/>
       <c r="E26" s="20"/>
@@ -2042,10 +2089,8 @@
       <c r="I26" s="20"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A27" s="26" t="s">
-        <v>35</v>
-      </c>
+    <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="29"/>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
       <c r="D27" s="20"/>
@@ -2056,9 +2101,9 @@
       <c r="I27" s="20"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="1:10" ht="15.75" customHeight="1">
+    <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="20"/>
@@ -2070,9 +2115,9 @@
       <c r="I28" s="20"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="1:10" ht="15.75" customHeight="1">
+    <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
@@ -2084,9 +2129,9 @@
       <c r="I29" s="20"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="1:10" ht="15.75" customHeight="1">
+    <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
@@ -2098,8 +2143,10 @@
       <c r="I30" s="20"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A31" s="20"/>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="26" t="s">
+        <v>38</v>
+      </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
       <c r="D31" s="20"/>
@@ -2110,7 +2157,7 @@
       <c r="I31" s="20"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="1:10" ht="15.75" customHeight="1">
+    <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="20"/>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
@@ -2122,7 +2169,7 @@
       <c r="I32" s="20"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1">
+    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="20"/>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -2134,7 +2181,7 @@
       <c r="I33" s="20"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1">
+    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="20"/>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -2146,7 +2193,7 @@
       <c r="I34" s="20"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1">
+    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="20"/>
       <c r="B35" s="20"/>
       <c r="C35" s="20"/>
@@ -2158,14 +2205,24 @@
       <c r="I35" s="20"/>
       <c r="J35" s="20"/>
     </row>
+    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F24" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F25" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/submission/Group Formation/STA380GroupForm.xlsx
+++ b/submission/Group Formation/STA380GroupForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/380_group_project/sta380-group-project/submission/Group Formation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14049626-01D0-FA4E-97C2-AAD5108E48B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB631556-2DD4-6145-9A90-EDA081907AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="4360" windowWidth="28400" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3560" yWindow="2440" windowWidth="28400" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -178,17 +178,19 @@
     <t>This project uses the Boston Housing Dataset to study the bootstrap estimation of linear regression coefficients (β₀, β₁),</t>
   </si>
   <si>
-    <t xml:space="preserve"> focusing on their mean and variance properties. </t>
-  </si>
-  <si>
-    <t>We will compare bootstrap-derived estimates with theoretical OLS results and examine how it affects estimation stability.</t>
-  </si>
-  <si>
     <t xml:space="preserve">We will use inverse-transformation method to simulate exponential and gamma distribution, including the </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>graph of true density. Outputing the mean and variance to the theoretical values.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">we will use the OLS estimates derived from the full dataset as our reference of true values. Then assess the bias and </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>standard error of bootstrap estimates relatie to the "true values".</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -412,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -471,6 +473,9 @@
       <alignment readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -482,12 +487,9 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -497,6 +499,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1744,11 +1751,11 @@
       <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="35" t="s">
+      <c r="B6" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="37"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -1771,13 +1778,13 @@
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="16"/>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="33" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="35"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
@@ -1831,27 +1838,27 @@
       <c r="A12" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="46"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="16"/>
-      <c r="B13" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="B13" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="44"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
@@ -1859,14 +1866,14 @@
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="16"/>
-      <c r="B14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+      <c r="B14" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="44"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
@@ -1919,13 +1926,13 @@
       <c r="A18" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="38"/>
+      <c r="B18" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="40"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
@@ -1934,7 +1941,7 @@
     <row r="19" spans="1:10" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="16"/>
       <c r="B19" s="41" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C19" s="42"/>
       <c r="D19" s="42"/>
@@ -1949,7 +1956,7 @@
       <c r="A20" s="10"/>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
-      <c r="D20" s="40"/>
+      <c r="D20" s="32"/>
       <c r="E20" s="11"/>
       <c r="F20" s="11"/>
       <c r="G20" s="19"/>
@@ -2214,11 +2221,14 @@
       <c r="F36" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B14:G14"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="B13:F13"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>

--- a/submission/Group Formation/STA380GroupForm.xlsx
+++ b/submission/Group Formation/STA380GroupForm.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/380_group_project/sta380-group-project/submission/Group Formation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB631556-2DD4-6145-9A90-EDA081907AA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A15E2A6-4229-C34F-A41D-2A916297FD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3560" yWindow="2440" windowWidth="28400" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1840" yWindow="2440" windowWidth="28400" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -175,9 +175,6 @@
     <t>Exponential + Gamma</t>
   </si>
   <si>
-    <t>This project uses the Boston Housing Dataset to study the bootstrap estimation of linear regression coefficients (β₀, β₁),</t>
-  </si>
-  <si>
     <t xml:space="preserve">We will use inverse-transformation method to simulate exponential and gamma distribution, including the </t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -186,11 +183,15 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">we will use the OLS estimates derived from the full dataset as our reference of true values. Then assess the bias and </t>
+    <t>This project uses the Boston Housing Dataset to study the bootstrap estimation of linear regression coefficients including</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>standard error of bootstrap estimates relatie to the "true values".</t>
+    <t xml:space="preserve">intercept and slope, we will use the OLS estimates derived from the full dataset as our reference of true values. </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Then assess the bias and standard error of bootstrap estimates relatie to the "true values".</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -414,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -499,11 +500,12 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1838,42 +1840,42 @@
       <c r="A12" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="47" t="s">
-        <v>46</v>
+      <c r="B12" s="36" t="s">
+        <v>48</v>
       </c>
       <c r="C12" s="47"/>
       <c r="D12" s="47"/>
       <c r="E12" s="47"/>
       <c r="F12" s="47"/>
-      <c r="G12" s="46"/>
+      <c r="G12" s="48"/>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="16"/>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
       <c r="F13" s="44"/>
-      <c r="G13" s="6"/>
+      <c r="G13" s="49"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="16"/>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="44" t="s">
         <v>50</v>
       </c>
       <c r="C14" s="45"/>
       <c r="D14" s="45"/>
       <c r="E14" s="45"/>
       <c r="F14" s="45"/>
-      <c r="G14" s="44"/>
+      <c r="G14" s="46"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
@@ -1927,7 +1929,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C18" s="39"/>
       <c r="D18" s="39"/>
@@ -1941,7 +1943,7 @@
     <row r="19" spans="1:10" ht="13.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="16"/>
       <c r="B19" s="41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" s="42"/>
       <c r="D19" s="42"/>
@@ -2228,7 +2230,7 @@
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B13:G13"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
